--- a/work/batch8/batch8-review.xlsx
+++ b/work/batch8/batch8-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maost\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\[01] Martin\[07] Claude Code\NS2-Spanish-Translation\work\batch8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62E13E24-B6C1-4A41-99B8-6C3D3B21EDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8872A663-FB8E-4B0C-8DE5-54EEF9340F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{ADFF9046-678F-48C9-80D6-8FE605C4BC13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{ADFF9046-678F-48C9-80D6-8FE605C4BC13}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="1843">
   <si>
     <t>Section</t>
   </si>
@@ -5585,6 +5585,9 @@
   </si>
   <si>
     <t>Flagged left</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -6145,7 +6148,7 @@
       </c>
       <c r="B10" s="14">
         <f>COUNTA(Review!J2:J539)</f>
-        <v>0</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -6154,7 +6157,7 @@
       </c>
       <c r="B11" s="14">
         <f>ROWS(Review!J2:J539)-COUNTA(Review!J2:J539)</f>
-        <v>538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -6163,7 +6166,7 @@
       </c>
       <c r="B12" s="14">
         <f>COUNTIFS(Review!G2:G539,"?*",Review!J2:J539,"")</f>
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6173,7 +6176,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF339A9-FF88-447A-9833-43357AC94A3F}">
-  <dimension ref="A1:L539"/>
+  <dimension ref="A1:L1048576"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -6190,7 +6193,7 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6248,7 +6251,9 @@
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
     </row>
@@ -6272,7 +6277,9 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
@@ -6296,7 +6303,9 @@
       <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
@@ -6320,7 +6329,9 @@
       <c r="G5" s="3"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
@@ -6348,7 +6359,9 @@
         <v>30</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
@@ -6372,7 +6385,9 @@
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
@@ -6402,7 +6417,9 @@
         <v>40</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
@@ -6426,7 +6443,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="6"/>
+      <c r="J9" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
@@ -6450,7 +6469,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
@@ -6474,7 +6495,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
     </row>
@@ -6498,7 +6521,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
@@ -6528,7 +6553,9 @@
       <c r="I13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="6"/>
+      <c r="J13" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
     </row>
@@ -6552,7 +6579,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="6"/>
+      <c r="J14" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
@@ -6576,7 +6605,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="6"/>
+      <c r="J15" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
     </row>
@@ -6600,7 +6631,9 @@
       <c r="G16" s="3"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
     </row>
@@ -6624,7 +6657,9 @@
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="6"/>
+      <c r="J17" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
     </row>
@@ -6648,7 +6683,9 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
     </row>
@@ -6672,7 +6709,9 @@
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="6"/>
+      <c r="J19" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
     </row>
@@ -6696,7 +6735,9 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="6"/>
+      <c r="J20" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
@@ -6720,7 +6761,9 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="6"/>
+      <c r="J21" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
@@ -6744,7 +6787,9 @@
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="6"/>
+      <c r="J22" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
@@ -6768,7 +6813,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
     </row>
@@ -6792,7 +6839,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="6"/>
+      <c r="J24" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
     </row>
@@ -6818,7 +6867,9 @@
       <c r="I25" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="6"/>
+      <c r="J25" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
     </row>
@@ -6842,7 +6893,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="6"/>
+      <c r="J26" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
     </row>
@@ -6870,7 +6923,9 @@
         <v>101</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="6"/>
+      <c r="J27" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
     </row>
@@ -6894,7 +6949,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="6"/>
+      <c r="J28" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
@@ -6918,7 +6975,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="6"/>
+      <c r="J29" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
@@ -6942,7 +7001,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
@@ -6966,7 +7027,9 @@
       <c r="G31" s="3"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="6"/>
+      <c r="J31" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
@@ -6990,7 +7053,9 @@
       <c r="G32" s="3"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="6"/>
+      <c r="J32" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
@@ -7014,7 +7079,9 @@
       <c r="G33" s="3"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="6"/>
+      <c r="J33" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
@@ -7038,7 +7105,9 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="6"/>
+      <c r="J34" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
@@ -7062,7 +7131,9 @@
       <c r="G35" s="3"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="6"/>
+      <c r="J35" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
@@ -7086,7 +7157,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="6"/>
+      <c r="J36" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
@@ -7110,7 +7183,9 @@
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="6"/>
+      <c r="J37" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
@@ -7134,7 +7209,9 @@
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="6"/>
+      <c r="J38" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
@@ -7160,7 +7237,9 @@
       <c r="I39" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="J39" s="6"/>
+      <c r="J39" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
@@ -7184,7 +7263,9 @@
       <c r="G40" s="3"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="6"/>
+      <c r="J40" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
@@ -7208,7 +7289,9 @@
       <c r="G41" s="3"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="6"/>
+      <c r="J41" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
@@ -7232,7 +7315,9 @@
       <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="6"/>
+      <c r="J42" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
@@ -7256,7 +7341,9 @@
       <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="6"/>
+      <c r="J43" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
@@ -7280,7 +7367,9 @@
       <c r="G44" s="3"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="6"/>
+      <c r="J44" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
@@ -7304,7 +7393,9 @@
       <c r="G45" s="3"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="6"/>
+      <c r="J45" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
@@ -7328,7 +7419,9 @@
       <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="6"/>
+      <c r="J46" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
@@ -7352,7 +7445,9 @@
       <c r="G47" s="3"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
@@ -7376,7 +7471,9 @@
       <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
@@ -7400,7 +7497,9 @@
       <c r="G49" s="3"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="6"/>
+      <c r="J49" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
@@ -7424,7 +7523,9 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="6"/>
+      <c r="J50" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
@@ -7450,7 +7551,9 @@
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="6"/>
+      <c r="J51" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
@@ -7474,7 +7577,9 @@
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="6"/>
+      <c r="J52" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
@@ -7498,7 +7603,9 @@
       <c r="G53" s="3"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="6"/>
+      <c r="J53" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
@@ -7524,7 +7631,9 @@
       <c r="G54" s="3"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="6"/>
+      <c r="J54" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
@@ -7550,7 +7659,9 @@
       <c r="G55" s="3"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="6"/>
+      <c r="J55" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
     </row>
@@ -7574,7 +7685,9 @@
       <c r="G56" s="3"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="6"/>
+      <c r="J56" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
@@ -7600,7 +7713,9 @@
       <c r="G57" s="3"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="6"/>
+      <c r="J57" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
     </row>
@@ -7626,7 +7741,9 @@
       <c r="G58" s="3"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="6"/>
+      <c r="J58" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
@@ -7652,7 +7769,9 @@
       <c r="G59" s="3"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="6"/>
+      <c r="J59" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
@@ -7678,7 +7797,9 @@
       <c r="G60" s="3"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="6"/>
+      <c r="J60" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
@@ -7708,7 +7829,9 @@
         <v>206</v>
       </c>
       <c r="I61" s="4"/>
-      <c r="J61" s="6"/>
+      <c r="J61" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
@@ -7738,7 +7861,9 @@
         <v>211</v>
       </c>
       <c r="I62" s="4"/>
-      <c r="J62" s="6"/>
+      <c r="J62" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
@@ -7764,7 +7889,9 @@
       <c r="G63" s="3"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="6"/>
+      <c r="J63" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
@@ -7790,7 +7917,9 @@
       <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="6"/>
+      <c r="J64" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
@@ -7816,7 +7945,9 @@
       <c r="G65" s="3"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="6"/>
+      <c r="J65" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
@@ -7840,7 +7971,9 @@
       <c r="G66" s="3"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="6"/>
+      <c r="J66" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
     </row>
@@ -7866,7 +7999,9 @@
       <c r="G67" s="3"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="6"/>
+      <c r="J67" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
     </row>
@@ -7898,7 +8033,9 @@
       <c r="I68" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="J68" s="6"/>
+      <c r="J68" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
@@ -7924,7 +8061,9 @@
       <c r="G69" s="3"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="6"/>
+      <c r="J69" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
@@ -7952,7 +8091,9 @@
         <v>238</v>
       </c>
       <c r="I70" s="4"/>
-      <c r="J70" s="6"/>
+      <c r="J70" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
@@ -7982,7 +8123,9 @@
         <v>243</v>
       </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="6"/>
+      <c r="J71" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
@@ -8012,7 +8155,9 @@
         <v>248</v>
       </c>
       <c r="I72" s="4"/>
-      <c r="J72" s="6"/>
+      <c r="J72" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
@@ -8042,7 +8187,9 @@
         <v>254</v>
       </c>
       <c r="I73" s="4"/>
-      <c r="J73" s="6"/>
+      <c r="J73" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
@@ -8072,7 +8219,9 @@
         <v>259</v>
       </c>
       <c r="I74" s="4"/>
-      <c r="J74" s="6"/>
+      <c r="J74" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
     </row>
@@ -8102,7 +8251,9 @@
         <v>264</v>
       </c>
       <c r="I75" s="4"/>
-      <c r="J75" s="6"/>
+      <c r="J75" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
     </row>
@@ -8132,7 +8283,9 @@
         <v>269</v>
       </c>
       <c r="I76" s="4"/>
-      <c r="J76" s="6"/>
+      <c r="J76" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
     </row>
@@ -8162,7 +8315,9 @@
         <v>274</v>
       </c>
       <c r="I77" s="4"/>
-      <c r="J77" s="6"/>
+      <c r="J77" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
     </row>
@@ -8192,7 +8347,9 @@
         <v>279</v>
       </c>
       <c r="I78" s="4"/>
-      <c r="J78" s="6"/>
+      <c r="J78" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
     </row>
@@ -8222,7 +8379,9 @@
         <v>284</v>
       </c>
       <c r="I79" s="4"/>
-      <c r="J79" s="6"/>
+      <c r="J79" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
@@ -8252,7 +8411,9 @@
         <v>289</v>
       </c>
       <c r="I80" s="4"/>
-      <c r="J80" s="6"/>
+      <c r="J80" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
     </row>
@@ -8282,7 +8443,9 @@
         <v>294</v>
       </c>
       <c r="I81" s="4"/>
-      <c r="J81" s="6"/>
+      <c r="J81" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
     </row>
@@ -8312,7 +8475,9 @@
         <v>299</v>
       </c>
       <c r="I82" s="4"/>
-      <c r="J82" s="6"/>
+      <c r="J82" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
     </row>
@@ -8342,7 +8507,9 @@
         <v>304</v>
       </c>
       <c r="I83" s="4"/>
-      <c r="J83" s="6"/>
+      <c r="J83" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
     </row>
@@ -8372,7 +8539,9 @@
         <v>309</v>
       </c>
       <c r="I84" s="4"/>
-      <c r="J84" s="6"/>
+      <c r="J84" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
     </row>
@@ -8402,7 +8571,9 @@
         <v>314</v>
       </c>
       <c r="I85" s="4"/>
-      <c r="J85" s="6"/>
+      <c r="J85" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
     </row>
@@ -8432,7 +8603,9 @@
         <v>319</v>
       </c>
       <c r="I86" s="4"/>
-      <c r="J86" s="6"/>
+      <c r="J86" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
     </row>
@@ -8462,7 +8635,9 @@
         <v>324</v>
       </c>
       <c r="I87" s="4"/>
-      <c r="J87" s="6"/>
+      <c r="J87" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
     </row>
@@ -8492,7 +8667,9 @@
         <v>329</v>
       </c>
       <c r="I88" s="4"/>
-      <c r="J88" s="6"/>
+      <c r="J88" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
     </row>
@@ -8522,7 +8699,9 @@
         <v>334</v>
       </c>
       <c r="I89" s="4"/>
-      <c r="J89" s="6"/>
+      <c r="J89" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
     </row>
@@ -8552,7 +8731,9 @@
         <v>339</v>
       </c>
       <c r="I90" s="4"/>
-      <c r="J90" s="6"/>
+      <c r="J90" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
     </row>
@@ -8582,7 +8763,9 @@
         <v>344</v>
       </c>
       <c r="I91" s="4"/>
-      <c r="J91" s="6"/>
+      <c r="J91" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
@@ -8612,7 +8795,9 @@
         <v>349</v>
       </c>
       <c r="I92" s="4"/>
-      <c r="J92" s="6"/>
+      <c r="J92" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
@@ -8642,7 +8827,9 @@
         <v>354</v>
       </c>
       <c r="I93" s="4"/>
-      <c r="J93" s="6"/>
+      <c r="J93" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
@@ -8672,7 +8859,9 @@
         <v>359</v>
       </c>
       <c r="I94" s="4"/>
-      <c r="J94" s="6"/>
+      <c r="J94" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
@@ -8702,7 +8891,9 @@
         <v>364</v>
       </c>
       <c r="I95" s="4"/>
-      <c r="J95" s="6"/>
+      <c r="J95" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
@@ -8732,7 +8923,9 @@
         <v>369</v>
       </c>
       <c r="I96" s="4"/>
-      <c r="J96" s="6"/>
+      <c r="J96" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
     </row>
@@ -8762,7 +8955,9 @@
         <v>374</v>
       </c>
       <c r="I97" s="4"/>
-      <c r="J97" s="6"/>
+      <c r="J97" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
     </row>
@@ -8792,7 +8987,9 @@
         <v>379</v>
       </c>
       <c r="I98" s="4"/>
-      <c r="J98" s="6"/>
+      <c r="J98" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
     </row>
@@ -8822,7 +9019,9 @@
         <v>384</v>
       </c>
       <c r="I99" s="4"/>
-      <c r="J99" s="6"/>
+      <c r="J99" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
     </row>
@@ -8852,7 +9051,9 @@
         <v>389</v>
       </c>
       <c r="I100" s="4"/>
-      <c r="J100" s="6"/>
+      <c r="J100" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
@@ -8882,7 +9083,9 @@
         <v>395</v>
       </c>
       <c r="I101" s="4"/>
-      <c r="J101" s="6"/>
+      <c r="J101" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
     </row>
@@ -8912,7 +9115,9 @@
         <v>400</v>
       </c>
       <c r="I102" s="4"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
     </row>
@@ -8942,7 +9147,9 @@
         <v>405</v>
       </c>
       <c r="I103" s="4"/>
-      <c r="J103" s="6"/>
+      <c r="J103" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
     </row>
@@ -8972,7 +9179,9 @@
         <v>410</v>
       </c>
       <c r="I104" s="4"/>
-      <c r="J104" s="6"/>
+      <c r="J104" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
     </row>
@@ -9002,7 +9211,9 @@
         <v>415</v>
       </c>
       <c r="I105" s="4"/>
-      <c r="J105" s="6"/>
+      <c r="J105" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
     </row>
@@ -9032,7 +9243,9 @@
         <v>420</v>
       </c>
       <c r="I106" s="4"/>
-      <c r="J106" s="6"/>
+      <c r="J106" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
     </row>
@@ -9062,7 +9275,9 @@
         <v>425</v>
       </c>
       <c r="I107" s="4"/>
-      <c r="J107" s="6"/>
+      <c r="J107" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
     </row>
@@ -9092,7 +9307,9 @@
         <v>430</v>
       </c>
       <c r="I108" s="4"/>
-      <c r="J108" s="6"/>
+      <c r="J108" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
     </row>
@@ -9122,7 +9339,9 @@
         <v>435</v>
       </c>
       <c r="I109" s="4"/>
-      <c r="J109" s="6"/>
+      <c r="J109" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
     </row>
@@ -9152,7 +9371,9 @@
         <v>440</v>
       </c>
       <c r="I110" s="4"/>
-      <c r="J110" s="6"/>
+      <c r="J110" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
     </row>
@@ -9182,7 +9403,9 @@
         <v>445</v>
       </c>
       <c r="I111" s="4"/>
-      <c r="J111" s="6"/>
+      <c r="J111" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
     </row>
@@ -9212,7 +9435,9 @@
         <v>389</v>
       </c>
       <c r="I112" s="4"/>
-      <c r="J112" s="6"/>
+      <c r="J112" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
     </row>
@@ -9242,7 +9467,9 @@
         <v>454</v>
       </c>
       <c r="I113" s="4"/>
-      <c r="J113" s="6"/>
+      <c r="J113" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
     </row>
@@ -9272,7 +9499,9 @@
         <v>459</v>
       </c>
       <c r="I114" s="4"/>
-      <c r="J114" s="6"/>
+      <c r="J114" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
     </row>
@@ -9302,7 +9531,9 @@
         <v>464</v>
       </c>
       <c r="I115" s="4"/>
-      <c r="J115" s="6"/>
+      <c r="J115" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
     </row>
@@ -9332,7 +9563,9 @@
         <v>339</v>
       </c>
       <c r="I116" s="4"/>
-      <c r="J116" s="6"/>
+      <c r="J116" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
     </row>
@@ -9362,7 +9595,9 @@
         <v>473</v>
       </c>
       <c r="I117" s="4"/>
-      <c r="J117" s="6"/>
+      <c r="J117" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
     </row>
@@ -9392,7 +9627,9 @@
         <v>478</v>
       </c>
       <c r="I118" s="4"/>
-      <c r="J118" s="6"/>
+      <c r="J118" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
     </row>
@@ -9422,7 +9659,9 @@
         <v>339</v>
       </c>
       <c r="I119" s="4"/>
-      <c r="J119" s="6"/>
+      <c r="J119" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
     </row>
@@ -9452,7 +9691,9 @@
         <v>487</v>
       </c>
       <c r="I120" s="4"/>
-      <c r="J120" s="6"/>
+      <c r="J120" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
     </row>
@@ -9482,7 +9723,9 @@
         <v>339</v>
       </c>
       <c r="I121" s="4"/>
-      <c r="J121" s="6"/>
+      <c r="J121" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
     </row>
@@ -9512,7 +9755,9 @@
         <v>496</v>
       </c>
       <c r="I122" s="4"/>
-      <c r="J122" s="6"/>
+      <c r="J122" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
     </row>
@@ -9538,7 +9783,9 @@
       <c r="G123" s="3"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-      <c r="J123" s="6"/>
+      <c r="J123" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
     </row>
@@ -9568,7 +9815,9 @@
         <v>505</v>
       </c>
       <c r="I124" s="4"/>
-      <c r="J124" s="6"/>
+      <c r="J124" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
     </row>
@@ -9598,7 +9847,9 @@
         <v>510</v>
       </c>
       <c r="I125" s="4"/>
-      <c r="J125" s="6"/>
+      <c r="J125" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
     </row>
@@ -9628,7 +9879,9 @@
         <v>515</v>
       </c>
       <c r="I126" s="4"/>
-      <c r="J126" s="6"/>
+      <c r="J126" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
     </row>
@@ -9658,7 +9911,9 @@
         <v>521</v>
       </c>
       <c r="I127" s="4"/>
-      <c r="J127" s="6"/>
+      <c r="J127" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
     </row>
@@ -9688,7 +9943,9 @@
         <v>526</v>
       </c>
       <c r="I128" s="4"/>
-      <c r="J128" s="6"/>
+      <c r="J128" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
     </row>
@@ -9718,7 +9975,9 @@
         <v>531</v>
       </c>
       <c r="I129" s="4"/>
-      <c r="J129" s="6"/>
+      <c r="J129" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
     </row>
@@ -9748,7 +10007,9 @@
         <v>536</v>
       </c>
       <c r="I130" s="4"/>
-      <c r="J130" s="6"/>
+      <c r="J130" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
     </row>
@@ -9778,7 +10039,9 @@
         <v>541</v>
       </c>
       <c r="I131" s="4"/>
-      <c r="J131" s="6"/>
+      <c r="J131" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
     </row>
@@ -9808,7 +10071,9 @@
         <v>546</v>
       </c>
       <c r="I132" s="4"/>
-      <c r="J132" s="6"/>
+      <c r="J132" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
     </row>
@@ -9838,7 +10103,9 @@
         <v>551</v>
       </c>
       <c r="I133" s="4"/>
-      <c r="J133" s="6"/>
+      <c r="J133" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
     </row>
@@ -9868,7 +10135,9 @@
         <v>556</v>
       </c>
       <c r="I134" s="4"/>
-      <c r="J134" s="6"/>
+      <c r="J134" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
     </row>
@@ -9898,7 +10167,9 @@
         <v>561</v>
       </c>
       <c r="I135" s="4"/>
-      <c r="J135" s="6"/>
+      <c r="J135" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
     </row>
@@ -9928,7 +10199,9 @@
         <v>566</v>
       </c>
       <c r="I136" s="4"/>
-      <c r="J136" s="6"/>
+      <c r="J136" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
     </row>
@@ -9958,7 +10231,9 @@
         <v>571</v>
       </c>
       <c r="I137" s="4"/>
-      <c r="J137" s="6"/>
+      <c r="J137" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
     </row>
@@ -9988,7 +10263,9 @@
         <v>576</v>
       </c>
       <c r="I138" s="4"/>
-      <c r="J138" s="6"/>
+      <c r="J138" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
     </row>
@@ -10018,7 +10295,9 @@
         <v>339</v>
       </c>
       <c r="I139" s="4"/>
-      <c r="J139" s="6"/>
+      <c r="J139" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
     </row>
@@ -10048,7 +10327,9 @@
         <v>211</v>
       </c>
       <c r="I140" s="4"/>
-      <c r="J140" s="6"/>
+      <c r="J140" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
     </row>
@@ -10078,7 +10359,9 @@
         <v>589</v>
       </c>
       <c r="I141" s="4"/>
-      <c r="J141" s="6"/>
+      <c r="J141" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
     </row>
@@ -10108,7 +10391,9 @@
         <v>594</v>
       </c>
       <c r="I142" s="4"/>
-      <c r="J142" s="6"/>
+      <c r="J142" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
     </row>
@@ -10138,7 +10423,9 @@
         <v>599</v>
       </c>
       <c r="I143" s="4"/>
-      <c r="J143" s="6"/>
+      <c r="J143" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
     </row>
@@ -10168,7 +10455,9 @@
         <v>604</v>
       </c>
       <c r="I144" s="4"/>
-      <c r="J144" s="6"/>
+      <c r="J144" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
     </row>
@@ -10198,7 +10487,9 @@
         <v>609</v>
       </c>
       <c r="I145" s="4"/>
-      <c r="J145" s="6"/>
+      <c r="J145" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
     </row>
@@ -10228,7 +10519,9 @@
         <v>614</v>
       </c>
       <c r="I146" s="4"/>
-      <c r="J146" s="6"/>
+      <c r="J146" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
     </row>
@@ -10258,7 +10551,9 @@
         <v>571</v>
       </c>
       <c r="I147" s="4"/>
-      <c r="J147" s="6"/>
+      <c r="J147" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
     </row>
@@ -10288,7 +10583,9 @@
         <v>623</v>
       </c>
       <c r="I148" s="4"/>
-      <c r="J148" s="6"/>
+      <c r="J148" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
     </row>
@@ -10318,7 +10615,9 @@
         <v>628</v>
       </c>
       <c r="I149" s="4"/>
-      <c r="J149" s="6"/>
+      <c r="J149" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
     </row>
@@ -10348,7 +10647,9 @@
         <v>633</v>
       </c>
       <c r="I150" s="4"/>
-      <c r="J150" s="6"/>
+      <c r="J150" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
     </row>
@@ -10378,7 +10679,9 @@
         <v>638</v>
       </c>
       <c r="I151" s="4"/>
-      <c r="J151" s="6"/>
+      <c r="J151" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
     </row>
@@ -10410,7 +10713,9 @@
       <c r="I152" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="J152" s="6"/>
+      <c r="J152" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
     </row>
@@ -10440,7 +10745,9 @@
         <v>649</v>
       </c>
       <c r="I153" s="4"/>
-      <c r="J153" s="6"/>
+      <c r="J153" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
     </row>
@@ -10470,7 +10777,9 @@
         <v>339</v>
       </c>
       <c r="I154" s="4"/>
-      <c r="J154" s="6"/>
+      <c r="J154" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
     </row>
@@ -10500,7 +10809,9 @@
         <v>658</v>
       </c>
       <c r="I155" s="4"/>
-      <c r="J155" s="6"/>
+      <c r="J155" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
     </row>
@@ -10530,7 +10841,9 @@
         <v>211</v>
       </c>
       <c r="I156" s="4"/>
-      <c r="J156" s="6"/>
+      <c r="J156" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
     </row>
@@ -10560,7 +10873,9 @@
         <v>667</v>
       </c>
       <c r="I157" s="4"/>
-      <c r="J157" s="6"/>
+      <c r="J157" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
     </row>
@@ -10590,7 +10905,9 @@
         <v>339</v>
       </c>
       <c r="I158" s="4"/>
-      <c r="J158" s="6"/>
+      <c r="J158" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
     </row>
@@ -10620,7 +10937,9 @@
         <v>676</v>
       </c>
       <c r="I159" s="4"/>
-      <c r="J159" s="6"/>
+      <c r="J159" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
     </row>
@@ -10650,7 +10969,9 @@
         <v>339</v>
       </c>
       <c r="I160" s="4"/>
-      <c r="J160" s="6"/>
+      <c r="J160" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
     </row>
@@ -10682,7 +11003,9 @@
       <c r="I161" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="J161" s="6"/>
+      <c r="J161" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
     </row>
@@ -10706,7 +11029,9 @@
       <c r="G162" s="3"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
-      <c r="J162" s="6"/>
+      <c r="J162" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
     </row>
@@ -10730,7 +11055,9 @@
       <c r="G163" s="3"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-      <c r="J163" s="6"/>
+      <c r="J163" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
     </row>
@@ -10754,7 +11081,9 @@
       <c r="G164" s="3"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="J164" s="6"/>
+      <c r="J164" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
     </row>
@@ -10778,7 +11107,9 @@
       <c r="G165" s="3"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
-      <c r="J165" s="6"/>
+      <c r="J165" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
     </row>
@@ -10802,7 +11133,9 @@
       <c r="G166" s="3"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
-      <c r="J166" s="6"/>
+      <c r="J166" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
     </row>
@@ -10826,7 +11159,9 @@
       <c r="G167" s="3"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
-      <c r="J167" s="6"/>
+      <c r="J167" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
     </row>
@@ -10850,7 +11185,9 @@
       <c r="G168" s="3"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
-      <c r="J168" s="6"/>
+      <c r="J168" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
     </row>
@@ -10874,7 +11211,9 @@
       <c r="G169" s="3"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="J169" s="6"/>
+      <c r="J169" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
     </row>
@@ -10898,7 +11237,9 @@
       <c r="G170" s="3"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
-      <c r="J170" s="6"/>
+      <c r="J170" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
     </row>
@@ -10922,7 +11263,9 @@
       <c r="G171" s="3"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="J171" s="6"/>
+      <c r="J171" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
     </row>
@@ -10946,7 +11289,9 @@
       <c r="G172" s="3"/>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
-      <c r="J172" s="6"/>
+      <c r="J172" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
     </row>
@@ -10970,7 +11315,9 @@
       <c r="G173" s="3"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-      <c r="J173" s="6"/>
+      <c r="J173" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
     </row>
@@ -10994,7 +11341,9 @@
       <c r="G174" s="3"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="J174" s="6"/>
+      <c r="J174" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
     </row>
@@ -11018,7 +11367,9 @@
       <c r="G175" s="3"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-      <c r="J175" s="6"/>
+      <c r="J175" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
     </row>
@@ -11042,7 +11393,9 @@
       <c r="G176" s="3"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="J176" s="6"/>
+      <c r="J176" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
     </row>
@@ -11066,7 +11419,9 @@
       <c r="G177" s="3"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-      <c r="J177" s="6"/>
+      <c r="J177" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
     </row>
@@ -11090,7 +11445,9 @@
       <c r="G178" s="3"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
-      <c r="J178" s="6"/>
+      <c r="J178" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
     </row>
@@ -11114,7 +11471,9 @@
       <c r="G179" s="3"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-      <c r="J179" s="6"/>
+      <c r="J179" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
     </row>
@@ -11138,7 +11497,9 @@
       <c r="G180" s="3"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
-      <c r="J180" s="6"/>
+      <c r="J180" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
     </row>
@@ -11162,7 +11523,9 @@
       <c r="G181" s="3"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-      <c r="J181" s="6"/>
+      <c r="J181" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
     </row>
@@ -11186,7 +11549,9 @@
       <c r="G182" s="3"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
-      <c r="J182" s="6"/>
+      <c r="J182" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
     </row>
@@ -11210,7 +11575,9 @@
       <c r="G183" s="3"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-      <c r="J183" s="6"/>
+      <c r="J183" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
     </row>
@@ -11234,7 +11601,9 @@
       <c r="G184" s="3"/>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
-      <c r="J184" s="6"/>
+      <c r="J184" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
     </row>
@@ -11258,7 +11627,9 @@
       <c r="G185" s="3"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-      <c r="J185" s="6"/>
+      <c r="J185" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
     </row>
@@ -11282,7 +11653,9 @@
       <c r="G186" s="3"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
-      <c r="J186" s="6"/>
+      <c r="J186" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
     </row>
@@ -11306,7 +11679,9 @@
       <c r="G187" s="3"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-      <c r="J187" s="6"/>
+      <c r="J187" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
     </row>
@@ -11330,7 +11705,9 @@
       <c r="G188" s="3"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
-      <c r="J188" s="6"/>
+      <c r="J188" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
     </row>
@@ -11354,7 +11731,9 @@
       <c r="G189" s="3"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
-      <c r="J189" s="6"/>
+      <c r="J189" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
     </row>
@@ -11378,7 +11757,9 @@
       <c r="G190" s="3"/>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
-      <c r="J190" s="6"/>
+      <c r="J190" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
     </row>
@@ -11402,7 +11783,9 @@
       <c r="G191" s="3"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-      <c r="J191" s="6"/>
+      <c r="J191" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
     </row>
@@ -11426,7 +11809,9 @@
       <c r="G192" s="3"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
-      <c r="J192" s="6"/>
+      <c r="J192" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
     </row>
@@ -11450,7 +11835,9 @@
       <c r="G193" s="3"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-      <c r="J193" s="6"/>
+      <c r="J193" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
     </row>
@@ -11474,7 +11861,9 @@
       <c r="G194" s="3"/>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
-      <c r="J194" s="6"/>
+      <c r="J194" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
     </row>
@@ -11498,7 +11887,9 @@
       <c r="G195" s="3"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
-      <c r="J195" s="6"/>
+      <c r="J195" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
     </row>
@@ -11522,7 +11913,9 @@
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
-      <c r="J196" s="6"/>
+      <c r="J196" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
     </row>
@@ -11546,7 +11939,9 @@
       <c r="G197" s="3"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
-      <c r="J197" s="6"/>
+      <c r="J197" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
     </row>
@@ -11570,7 +11965,9 @@
       <c r="G198" s="3"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
-      <c r="J198" s="6"/>
+      <c r="J198" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
     </row>
@@ -11594,7 +11991,9 @@
       <c r="G199" s="3"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-      <c r="J199" s="6"/>
+      <c r="J199" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
     </row>
@@ -11618,7 +12017,9 @@
       <c r="G200" s="3"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
-      <c r="J200" s="6"/>
+      <c r="J200" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
     </row>
@@ -11642,7 +12043,9 @@
       <c r="G201" s="3"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
-      <c r="J201" s="6"/>
+      <c r="J201" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
     </row>
@@ -11666,7 +12069,9 @@
       <c r="G202" s="3"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
-      <c r="J202" s="6"/>
+      <c r="J202" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
     </row>
@@ -11690,7 +12095,9 @@
       <c r="G203" s="3"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
-      <c r="J203" s="6"/>
+      <c r="J203" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
     </row>
@@ -11714,7 +12121,9 @@
       <c r="G204" s="3"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
-      <c r="J204" s="6"/>
+      <c r="J204" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
     </row>
@@ -11738,7 +12147,9 @@
       <c r="G205" s="3"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-      <c r="J205" s="6"/>
+      <c r="J205" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
     </row>
@@ -11762,7 +12173,9 @@
       <c r="G206" s="3"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
-      <c r="J206" s="6"/>
+      <c r="J206" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
     </row>
@@ -11786,7 +12199,9 @@
       <c r="G207" s="3"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
-      <c r="J207" s="6"/>
+      <c r="J207" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
     </row>
@@ -11810,7 +12225,9 @@
       <c r="G208" s="3"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
-      <c r="J208" s="6"/>
+      <c r="J208" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
     </row>
@@ -11834,7 +12251,9 @@
       <c r="G209" s="3"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-      <c r="J209" s="6"/>
+      <c r="J209" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
     </row>
@@ -11858,7 +12277,9 @@
       <c r="G210" s="3"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
-      <c r="J210" s="6"/>
+      <c r="J210" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
     </row>
@@ -11882,7 +12303,9 @@
       <c r="G211" s="3"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
-      <c r="J211" s="6"/>
+      <c r="J211" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
     </row>
@@ -11906,7 +12329,9 @@
       <c r="G212" s="3"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
-      <c r="J212" s="6"/>
+      <c r="J212" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
     </row>
@@ -11930,7 +12355,9 @@
       <c r="G213" s="3"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-      <c r="J213" s="6"/>
+      <c r="J213" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
     </row>
@@ -11954,7 +12381,9 @@
       <c r="G214" s="3"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
-      <c r="J214" s="6"/>
+      <c r="J214" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
     </row>
@@ -11978,7 +12407,9 @@
       <c r="G215" s="3"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
-      <c r="J215" s="6"/>
+      <c r="J215" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
     </row>
@@ -12002,7 +12433,9 @@
       <c r="G216" s="3"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
-      <c r="J216" s="6"/>
+      <c r="J216" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
     </row>
@@ -12026,7 +12459,9 @@
       <c r="G217" s="3"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-      <c r="J217" s="6"/>
+      <c r="J217" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
     </row>
@@ -12050,7 +12485,9 @@
       <c r="G218" s="3"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
-      <c r="J218" s="6"/>
+      <c r="J218" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
     </row>
@@ -12074,7 +12511,9 @@
       <c r="G219" s="3"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
-      <c r="J219" s="6"/>
+      <c r="J219" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
     </row>
@@ -12098,7 +12537,9 @@
       <c r="G220" s="3"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
-      <c r="J220" s="6"/>
+      <c r="J220" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
     </row>
@@ -12122,7 +12563,9 @@
       <c r="G221" s="3"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
-      <c r="J221" s="6"/>
+      <c r="J221" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
     </row>
@@ -12146,7 +12589,9 @@
       <c r="G222" s="3"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
-      <c r="J222" s="6"/>
+      <c r="J222" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
     </row>
@@ -12170,7 +12615,9 @@
       <c r="G223" s="3"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
-      <c r="J223" s="6"/>
+      <c r="J223" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
     </row>
@@ -12194,7 +12641,9 @@
       <c r="G224" s="3"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
-      <c r="J224" s="6"/>
+      <c r="J224" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
     </row>
@@ -12218,7 +12667,9 @@
       <c r="G225" s="3"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
-      <c r="J225" s="6"/>
+      <c r="J225" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
     </row>
@@ -12242,7 +12693,9 @@
       <c r="G226" s="3"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
-      <c r="J226" s="6"/>
+      <c r="J226" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
     </row>
@@ -12266,7 +12719,9 @@
       <c r="G227" s="3"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
-      <c r="J227" s="6"/>
+      <c r="J227" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
     </row>
@@ -12290,7 +12745,9 @@
       <c r="G228" s="3"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
-      <c r="J228" s="6"/>
+      <c r="J228" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
     </row>
@@ -12314,7 +12771,9 @@
       <c r="G229" s="3"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-      <c r="J229" s="6"/>
+      <c r="J229" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
     </row>
@@ -12338,7 +12797,9 @@
       <c r="G230" s="3"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
-      <c r="J230" s="6"/>
+      <c r="J230" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
     </row>
@@ -12362,7 +12823,9 @@
       <c r="G231" s="3"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
-      <c r="J231" s="6"/>
+      <c r="J231" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
     </row>
@@ -12386,7 +12849,9 @@
       <c r="G232" s="3"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
-      <c r="J232" s="6"/>
+      <c r="J232" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
     </row>
@@ -12410,7 +12875,9 @@
       <c r="G233" s="3"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
-      <c r="J233" s="6"/>
+      <c r="J233" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
     </row>
@@ -12434,7 +12901,9 @@
       <c r="G234" s="3"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
-      <c r="J234" s="6"/>
+      <c r="J234" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
     </row>
@@ -12458,7 +12927,9 @@
       <c r="G235" s="3"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
-      <c r="J235" s="6"/>
+      <c r="J235" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
     </row>
@@ -12482,7 +12953,9 @@
       <c r="G236" s="3"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
-      <c r="J236" s="6"/>
+      <c r="J236" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
     </row>
@@ -12506,7 +12979,9 @@
       <c r="G237" s="3"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
-      <c r="J237" s="6"/>
+      <c r="J237" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
     </row>
@@ -12530,7 +13005,9 @@
       <c r="G238" s="3"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
-      <c r="J238" s="6"/>
+      <c r="J238" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
     </row>
@@ -12554,7 +13031,9 @@
       <c r="G239" s="3"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-      <c r="J239" s="6"/>
+      <c r="J239" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
     </row>
@@ -12578,7 +13057,9 @@
       <c r="G240" s="3"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
-      <c r="J240" s="6"/>
+      <c r="J240" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
     </row>
@@ -12602,7 +13083,9 @@
       <c r="G241" s="3"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
-      <c r="J241" s="6"/>
+      <c r="J241" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
     </row>
@@ -12626,7 +13109,9 @@
       <c r="G242" s="3"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
-      <c r="J242" s="6"/>
+      <c r="J242" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
     </row>
@@ -12650,7 +13135,9 @@
       <c r="G243" s="3"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
-      <c r="J243" s="6"/>
+      <c r="J243" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
     </row>
@@ -12674,7 +13161,9 @@
       <c r="G244" s="3"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
-      <c r="J244" s="6"/>
+      <c r="J244" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
     </row>
@@ -12698,7 +13187,9 @@
       <c r="G245" s="3"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-      <c r="J245" s="6"/>
+      <c r="J245" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
     </row>
@@ -12722,7 +13213,9 @@
       <c r="G246" s="3"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
-      <c r="J246" s="6"/>
+      <c r="J246" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
     </row>
@@ -12746,7 +13239,9 @@
       <c r="G247" s="3"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-      <c r="J247" s="6"/>
+      <c r="J247" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
     </row>
@@ -12770,7 +13265,9 @@
       <c r="G248" s="3"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
-      <c r="J248" s="6"/>
+      <c r="J248" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
     </row>
@@ -12794,7 +13291,9 @@
       <c r="G249" s="3"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
-      <c r="J249" s="6"/>
+      <c r="J249" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
     </row>
@@ -12818,7 +13317,9 @@
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
-      <c r="J250" s="6"/>
+      <c r="J250" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
     </row>
@@ -12842,7 +13343,9 @@
       <c r="G251" s="3"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
-      <c r="J251" s="6"/>
+      <c r="J251" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
     </row>
@@ -12866,7 +13369,9 @@
       <c r="G252" s="3"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
-      <c r="J252" s="6"/>
+      <c r="J252" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
     </row>
@@ -12890,7 +13395,9 @@
       <c r="G253" s="3"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
-      <c r="J253" s="6"/>
+      <c r="J253" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
     </row>
@@ -12914,7 +13421,9 @@
       <c r="G254" s="3"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
-      <c r="J254" s="6"/>
+      <c r="J254" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
     </row>
@@ -12938,7 +13447,9 @@
       <c r="G255" s="3"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-      <c r="J255" s="6"/>
+      <c r="J255" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
     </row>
@@ -12962,7 +13473,9 @@
       <c r="G256" s="3"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
-      <c r="J256" s="6"/>
+      <c r="J256" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
     </row>
@@ -12986,7 +13499,9 @@
       <c r="G257" s="3"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
-      <c r="J257" s="6"/>
+      <c r="J257" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
     </row>
@@ -13010,7 +13525,9 @@
       <c r="G258" s="3"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
-      <c r="J258" s="6"/>
+      <c r="J258" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
     </row>
@@ -13034,7 +13551,9 @@
       <c r="G259" s="3"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
-      <c r="J259" s="6"/>
+      <c r="J259" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
     </row>
@@ -13058,7 +13577,9 @@
       <c r="G260" s="3"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
-      <c r="J260" s="6"/>
+      <c r="J260" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
     </row>
@@ -13082,7 +13603,9 @@
       <c r="G261" s="3"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
-      <c r="J261" s="6"/>
+      <c r="J261" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
     </row>
@@ -13106,7 +13629,9 @@
       <c r="G262" s="3"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
-      <c r="J262" s="6"/>
+      <c r="J262" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
     </row>
@@ -13130,7 +13655,9 @@
       <c r="G263" s="3"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
-      <c r="J263" s="6"/>
+      <c r="J263" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
     </row>
@@ -13154,7 +13681,9 @@
       <c r="G264" s="3"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
-      <c r="J264" s="6"/>
+      <c r="J264" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
     </row>
@@ -13178,7 +13707,9 @@
       <c r="G265" s="3"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
-      <c r="J265" s="6"/>
+      <c r="J265" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
     </row>
@@ -13202,7 +13733,9 @@
       <c r="G266" s="3"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
-      <c r="J266" s="6"/>
+      <c r="J266" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
     </row>
@@ -13226,7 +13759,9 @@
       <c r="G267" s="3"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-      <c r="J267" s="6"/>
+      <c r="J267" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
     </row>
@@ -13250,7 +13785,9 @@
       <c r="G268" s="3"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
-      <c r="J268" s="6"/>
+      <c r="J268" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
     </row>
@@ -13274,7 +13811,9 @@
       <c r="G269" s="3"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-      <c r="J269" s="6"/>
+      <c r="J269" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
     </row>
@@ -13298,7 +13837,9 @@
       <c r="G270" s="3"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
-      <c r="J270" s="6"/>
+      <c r="J270" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
     </row>
@@ -13322,7 +13863,9 @@
       <c r="G271" s="3"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-      <c r="J271" s="6"/>
+      <c r="J271" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
     </row>
@@ -13346,7 +13889,9 @@
       <c r="G272" s="3"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
-      <c r="J272" s="6"/>
+      <c r="J272" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
     </row>
@@ -13370,7 +13915,9 @@
       <c r="G273" s="3"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
-      <c r="J273" s="6"/>
+      <c r="J273" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
     </row>
@@ -13394,7 +13941,9 @@
       <c r="G274" s="3"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
-      <c r="J274" s="6"/>
+      <c r="J274" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
     </row>
@@ -13418,7 +13967,9 @@
       <c r="G275" s="3"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
-      <c r="J275" s="6"/>
+      <c r="J275" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
     </row>
@@ -13442,7 +13993,9 @@
       <c r="G276" s="3"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
-      <c r="J276" s="6"/>
+      <c r="J276" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
     </row>
@@ -13466,7 +14019,9 @@
       <c r="G277" s="3"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-      <c r="J277" s="6"/>
+      <c r="J277" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
     </row>
@@ -13490,7 +14045,9 @@
       <c r="G278" s="3"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
-      <c r="J278" s="6"/>
+      <c r="J278" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
     </row>
@@ -13514,7 +14071,9 @@
       <c r="G279" s="3"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-      <c r="J279" s="6"/>
+      <c r="J279" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
     </row>
@@ -13538,7 +14097,9 @@
       <c r="G280" s="3"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
-      <c r="J280" s="6"/>
+      <c r="J280" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
     </row>
@@ -13562,7 +14123,9 @@
       <c r="G281" s="3"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
-      <c r="J281" s="6"/>
+      <c r="J281" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
     </row>
@@ -13586,7 +14149,9 @@
       <c r="G282" s="3"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
-      <c r="J282" s="6"/>
+      <c r="J282" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
     </row>
@@ -13610,7 +14175,9 @@
       <c r="G283" s="3"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
-      <c r="J283" s="6"/>
+      <c r="J283" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
     </row>
@@ -13634,7 +14201,9 @@
       <c r="G284" s="3"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
-      <c r="J284" s="6"/>
+      <c r="J284" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
     </row>
@@ -13658,7 +14227,9 @@
       <c r="G285" s="3"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-      <c r="J285" s="6"/>
+      <c r="J285" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
     </row>
@@ -13682,7 +14253,9 @@
       <c r="G286" s="3"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
-      <c r="J286" s="6"/>
+      <c r="J286" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
     </row>
@@ -13706,7 +14279,9 @@
       <c r="G287" s="3"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
-      <c r="J287" s="6"/>
+      <c r="J287" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
     </row>
@@ -13730,7 +14305,9 @@
       <c r="G288" s="3"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
-      <c r="J288" s="6"/>
+      <c r="J288" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
     </row>
@@ -13754,7 +14331,9 @@
       <c r="G289" s="3"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
-      <c r="J289" s="6"/>
+      <c r="J289" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
     </row>
@@ -13778,7 +14357,9 @@
       <c r="G290" s="3"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
-      <c r="J290" s="6"/>
+      <c r="J290" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
     </row>
@@ -13802,7 +14383,9 @@
       <c r="G291" s="3"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
-      <c r="J291" s="6"/>
+      <c r="J291" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
     </row>
@@ -13826,7 +14409,9 @@
       <c r="G292" s="3"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
-      <c r="J292" s="6"/>
+      <c r="J292" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
     </row>
@@ -13850,7 +14435,9 @@
       <c r="G293" s="3"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-      <c r="J293" s="6"/>
+      <c r="J293" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
     </row>
@@ -13874,7 +14461,9 @@
       <c r="G294" s="3"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
-      <c r="J294" s="6"/>
+      <c r="J294" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
     </row>
@@ -13898,7 +14487,9 @@
       <c r="G295" s="3"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
-      <c r="J295" s="6"/>
+      <c r="J295" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
     </row>
@@ -13922,7 +14513,9 @@
       <c r="G296" s="3"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
-      <c r="J296" s="6"/>
+      <c r="J296" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
     </row>
@@ -13946,7 +14539,9 @@
       <c r="G297" s="3"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-      <c r="J297" s="6"/>
+      <c r="J297" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
     </row>
@@ -13970,7 +14565,9 @@
       <c r="G298" s="3"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
-      <c r="J298" s="6"/>
+      <c r="J298" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
     </row>
@@ -13994,7 +14591,9 @@
       <c r="G299" s="3"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-      <c r="J299" s="6"/>
+      <c r="J299" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
     </row>
@@ -14018,7 +14617,9 @@
       <c r="G300" s="3"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
-      <c r="J300" s="6"/>
+      <c r="J300" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
     </row>
@@ -14042,7 +14643,9 @@
       <c r="G301" s="3"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
-      <c r="J301" s="6"/>
+      <c r="J301" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
     </row>
@@ -14066,7 +14669,9 @@
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
-      <c r="J302" s="6"/>
+      <c r="J302" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
     </row>
@@ -14090,7 +14695,9 @@
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-      <c r="J303" s="6"/>
+      <c r="J303" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
     </row>
@@ -14114,7 +14721,9 @@
       <c r="G304" s="3"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
-      <c r="J304" s="6"/>
+      <c r="J304" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
     </row>
@@ -14140,7 +14749,9 @@
       <c r="I305" s="10" t="s">
         <v>1120</v>
       </c>
-      <c r="J305" s="6"/>
+      <c r="J305" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
     </row>
@@ -14164,7 +14775,9 @@
       <c r="G306" s="3"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
-      <c r="J306" s="6"/>
+      <c r="J306" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
     </row>
@@ -14188,7 +14801,9 @@
       <c r="G307" s="3"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
-      <c r="J307" s="6"/>
+      <c r="J307" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
     </row>
@@ -14212,7 +14827,9 @@
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
-      <c r="J308" s="6"/>
+      <c r="J308" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
     </row>
@@ -14236,7 +14853,9 @@
       <c r="G309" s="3"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-      <c r="J309" s="6"/>
+      <c r="J309" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
     </row>
@@ -14260,7 +14879,9 @@
       <c r="G310" s="3"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
-      <c r="J310" s="6"/>
+      <c r="J310" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
     </row>
@@ -14284,7 +14905,9 @@
       <c r="G311" s="3"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-      <c r="J311" s="6"/>
+      <c r="J311" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
     </row>
@@ -14308,7 +14931,9 @@
       <c r="G312" s="3"/>
       <c r="H312" s="4"/>
       <c r="I312" s="4"/>
-      <c r="J312" s="6"/>
+      <c r="J312" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
     </row>
@@ -14332,7 +14957,9 @@
       <c r="G313" s="3"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-      <c r="J313" s="6"/>
+      <c r="J313" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
     </row>
@@ -14356,7 +14983,9 @@
       <c r="G314" s="3"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
-      <c r="J314" s="6"/>
+      <c r="J314" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
     </row>
@@ -14380,7 +15009,9 @@
       <c r="G315" s="3"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-      <c r="J315" s="6"/>
+      <c r="J315" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
     </row>
@@ -14404,7 +15035,9 @@
       <c r="G316" s="3"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
-      <c r="J316" s="6"/>
+      <c r="J316" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
     </row>
@@ -14428,7 +15061,9 @@
       <c r="G317" s="3"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-      <c r="J317" s="6"/>
+      <c r="J317" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
     </row>
@@ -14452,7 +15087,9 @@
       <c r="G318" s="3"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
-      <c r="J318" s="6"/>
+      <c r="J318" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
     </row>
@@ -14476,7 +15113,9 @@
       <c r="G319" s="3"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-      <c r="J319" s="6"/>
+      <c r="J319" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
     </row>
@@ -14500,7 +15139,9 @@
       <c r="G320" s="3"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
-      <c r="J320" s="6"/>
+      <c r="J320" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
     </row>
@@ -14524,7 +15165,9 @@
       <c r="G321" s="3"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
-      <c r="J321" s="6"/>
+      <c r="J321" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
     </row>
@@ -14548,7 +15191,9 @@
       <c r="G322" s="3"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
-      <c r="J322" s="6"/>
+      <c r="J322" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
     </row>
@@ -14572,7 +15217,9 @@
       <c r="G323" s="3"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-      <c r="J323" s="6"/>
+      <c r="J323" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
     </row>
@@ -14596,7 +15243,9 @@
       <c r="G324" s="3"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
-      <c r="J324" s="6"/>
+      <c r="J324" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
     </row>
@@ -14620,7 +15269,9 @@
       <c r="G325" s="3"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-      <c r="J325" s="6"/>
+      <c r="J325" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
     </row>
@@ -14644,7 +15295,9 @@
       <c r="G326" s="3"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
-      <c r="J326" s="6"/>
+      <c r="J326" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
     </row>
@@ -14668,7 +15321,9 @@
       <c r="G327" s="3"/>
       <c r="H327" s="4"/>
       <c r="I327" s="4"/>
-      <c r="J327" s="6"/>
+      <c r="J327" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
     </row>
@@ -14692,7 +15347,9 @@
       <c r="G328" s="3"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
-      <c r="J328" s="6"/>
+      <c r="J328" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
     </row>
@@ -14716,7 +15373,9 @@
       <c r="G329" s="3"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-      <c r="J329" s="6"/>
+      <c r="J329" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
     </row>
@@ -14740,7 +15399,9 @@
       <c r="G330" s="3"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="6"/>
+      <c r="J330" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
     </row>
@@ -14764,7 +15425,9 @@
       <c r="G331" s="3"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-      <c r="J331" s="6"/>
+      <c r="J331" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
     </row>
@@ -14788,7 +15451,9 @@
       <c r="G332" s="3"/>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
-      <c r="J332" s="6"/>
+      <c r="J332" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
     </row>
@@ -14812,7 +15477,9 @@
       <c r="G333" s="3"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
-      <c r="J333" s="6"/>
+      <c r="J333" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
     </row>
@@ -14836,7 +15503,9 @@
       <c r="G334" s="3"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
-      <c r="J334" s="6"/>
+      <c r="J334" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
     </row>
@@ -14860,7 +15529,9 @@
       <c r="G335" s="3"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-      <c r="J335" s="6"/>
+      <c r="J335" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
     </row>
@@ -14884,7 +15555,9 @@
       <c r="G336" s="3"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
-      <c r="J336" s="6"/>
+      <c r="J336" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
     </row>
@@ -14908,7 +15581,9 @@
       <c r="G337" s="3"/>
       <c r="H337" s="4"/>
       <c r="I337" s="4"/>
-      <c r="J337" s="6"/>
+      <c r="J337" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
     </row>
@@ -14932,7 +15607,9 @@
       <c r="G338" s="3"/>
       <c r="H338" s="4"/>
       <c r="I338" s="4"/>
-      <c r="J338" s="6"/>
+      <c r="J338" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
     </row>
@@ -14956,7 +15633,9 @@
       <c r="G339" s="3"/>
       <c r="H339" s="4"/>
       <c r="I339" s="4"/>
-      <c r="J339" s="6"/>
+      <c r="J339" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
     </row>
@@ -14980,7 +15659,9 @@
       <c r="G340" s="3"/>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
-      <c r="J340" s="6"/>
+      <c r="J340" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
     </row>
@@ -15004,7 +15685,9 @@
       <c r="G341" s="3"/>
       <c r="H341" s="4"/>
       <c r="I341" s="4"/>
-      <c r="J341" s="6"/>
+      <c r="J341" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
     </row>
@@ -15028,7 +15711,9 @@
       <c r="G342" s="3"/>
       <c r="H342" s="4"/>
       <c r="I342" s="4"/>
-      <c r="J342" s="6"/>
+      <c r="J342" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
     </row>
@@ -15052,7 +15737,9 @@
       <c r="G343" s="3"/>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
-      <c r="J343" s="6"/>
+      <c r="J343" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
     </row>
@@ -15076,7 +15763,9 @@
       <c r="G344" s="3"/>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
-      <c r="J344" s="6"/>
+      <c r="J344" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
     </row>
@@ -15100,7 +15789,9 @@
       <c r="G345" s="3"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-      <c r="J345" s="6"/>
+      <c r="J345" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
     </row>
@@ -15124,7 +15815,9 @@
       <c r="G346" s="3"/>
       <c r="H346" s="4"/>
       <c r="I346" s="4"/>
-      <c r="J346" s="6"/>
+      <c r="J346" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
     </row>
@@ -15150,7 +15843,9 @@
       <c r="I347" s="10" t="s">
         <v>1247</v>
       </c>
-      <c r="J347" s="6"/>
+      <c r="J347" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
     </row>
@@ -15174,7 +15869,9 @@
       <c r="G348" s="3"/>
       <c r="H348" s="4"/>
       <c r="I348" s="4"/>
-      <c r="J348" s="6"/>
+      <c r="J348" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
     </row>
@@ -15198,7 +15895,9 @@
       <c r="G349" s="3"/>
       <c r="H349" s="4"/>
       <c r="I349" s="4"/>
-      <c r="J349" s="6"/>
+      <c r="J349" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
     </row>
@@ -15222,7 +15921,9 @@
       <c r="G350" s="3"/>
       <c r="H350" s="4"/>
       <c r="I350" s="4"/>
-      <c r="J350" s="6"/>
+      <c r="J350" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
     </row>
@@ -15246,7 +15947,9 @@
       <c r="G351" s="3"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
-      <c r="J351" s="6"/>
+      <c r="J351" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
     </row>
@@ -15270,7 +15973,9 @@
       <c r="G352" s="3"/>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
-      <c r="J352" s="6"/>
+      <c r="J352" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
     </row>
@@ -15294,7 +15999,9 @@
       <c r="G353" s="3"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-      <c r="J353" s="6"/>
+      <c r="J353" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
     </row>
@@ -15318,7 +16025,9 @@
       <c r="G354" s="3"/>
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
-      <c r="J354" s="6"/>
+      <c r="J354" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
     </row>
@@ -15342,7 +16051,9 @@
       <c r="G355" s="3"/>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
-      <c r="J355" s="6"/>
+      <c r="J355" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
     </row>
@@ -15366,7 +16077,9 @@
       <c r="G356" s="3"/>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
-      <c r="J356" s="6"/>
+      <c r="J356" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
     </row>
@@ -15390,7 +16103,9 @@
       <c r="G357" s="3"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-      <c r="J357" s="6"/>
+      <c r="J357" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
     </row>
@@ -15414,7 +16129,9 @@
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
-      <c r="J358" s="6"/>
+      <c r="J358" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
     </row>
@@ -15438,7 +16155,9 @@
       <c r="G359" s="3"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-      <c r="J359" s="6"/>
+      <c r="J359" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
     </row>
@@ -15462,7 +16181,9 @@
       <c r="G360" s="3"/>
       <c r="H360" s="4"/>
       <c r="I360" s="4"/>
-      <c r="J360" s="6"/>
+      <c r="J360" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
     </row>
@@ -15486,7 +16207,9 @@
       <c r="G361" s="3"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
-      <c r="J361" s="6"/>
+      <c r="J361" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
     </row>
@@ -15510,7 +16233,9 @@
       <c r="G362" s="3"/>
       <c r="H362" s="4"/>
       <c r="I362" s="4"/>
-      <c r="J362" s="6"/>
+      <c r="J362" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
     </row>
@@ -15534,7 +16259,9 @@
       <c r="G363" s="3"/>
       <c r="H363" s="4"/>
       <c r="I363" s="4"/>
-      <c r="J363" s="6"/>
+      <c r="J363" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
     </row>
@@ -15558,7 +16285,9 @@
       <c r="G364" s="3"/>
       <c r="H364" s="4"/>
       <c r="I364" s="4"/>
-      <c r="J364" s="6"/>
+      <c r="J364" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
     </row>
@@ -15582,7 +16311,9 @@
       <c r="G365" s="3"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
-      <c r="J365" s="6"/>
+      <c r="J365" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
     </row>
@@ -15606,7 +16337,9 @@
       <c r="G366" s="3"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
-      <c r="J366" s="6"/>
+      <c r="J366" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
     </row>
@@ -15630,7 +16363,9 @@
       <c r="G367" s="3"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
-      <c r="J367" s="6"/>
+      <c r="J367" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
     </row>
@@ -15654,7 +16389,9 @@
       <c r="G368" s="3"/>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
-      <c r="J368" s="6"/>
+      <c r="J368" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
     </row>
@@ -15678,7 +16415,9 @@
       <c r="G369" s="3"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
-      <c r="J369" s="6"/>
+      <c r="J369" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
     </row>
@@ -15702,7 +16441,9 @@
       <c r="G370" s="3"/>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
-      <c r="J370" s="6"/>
+      <c r="J370" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
     </row>
@@ -15726,7 +16467,9 @@
       <c r="G371" s="3"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-      <c r="J371" s="6"/>
+      <c r="J371" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
     </row>
@@ -15750,7 +16493,9 @@
       <c r="G372" s="3"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
-      <c r="J372" s="6"/>
+      <c r="J372" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
     </row>
@@ -15774,7 +16519,9 @@
       <c r="G373" s="3"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-      <c r="J373" s="6"/>
+      <c r="J373" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
     </row>
@@ -15798,7 +16545,9 @@
       <c r="G374" s="3"/>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
-      <c r="J374" s="6"/>
+      <c r="J374" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
     </row>
@@ -15822,7 +16571,9 @@
       <c r="G375" s="3"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-      <c r="J375" s="6"/>
+      <c r="J375" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
     </row>
@@ -15846,7 +16597,9 @@
       <c r="G376" s="3"/>
       <c r="H376" s="4"/>
       <c r="I376" s="4"/>
-      <c r="J376" s="6"/>
+      <c r="J376" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
     </row>
@@ -15870,7 +16623,9 @@
       <c r="G377" s="3"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-      <c r="J377" s="6"/>
+      <c r="J377" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
     </row>
@@ -15894,7 +16649,9 @@
       <c r="G378" s="3"/>
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
-      <c r="J378" s="6"/>
+      <c r="J378" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
     </row>
@@ -15918,7 +16675,9 @@
       <c r="G379" s="3"/>
       <c r="H379" s="4"/>
       <c r="I379" s="4"/>
-      <c r="J379" s="6"/>
+      <c r="J379" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
     </row>
@@ -15942,7 +16701,9 @@
       <c r="G380" s="3"/>
       <c r="H380" s="4"/>
       <c r="I380" s="4"/>
-      <c r="J380" s="6"/>
+      <c r="J380" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
     </row>
@@ -15966,7 +16727,9 @@
       <c r="G381" s="3"/>
       <c r="H381" s="4"/>
       <c r="I381" s="4"/>
-      <c r="J381" s="6"/>
+      <c r="J381" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
     </row>
@@ -15990,7 +16753,9 @@
       <c r="G382" s="3"/>
       <c r="H382" s="4"/>
       <c r="I382" s="4"/>
-      <c r="J382" s="6"/>
+      <c r="J382" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
     </row>
@@ -16014,7 +16779,9 @@
       <c r="G383" s="3"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
-      <c r="J383" s="6"/>
+      <c r="J383" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
     </row>
@@ -16038,7 +16805,9 @@
       <c r="G384" s="3"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
-      <c r="J384" s="6"/>
+      <c r="J384" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
     </row>
@@ -16062,7 +16831,9 @@
       <c r="G385" s="3"/>
       <c r="H385" s="4"/>
       <c r="I385" s="4"/>
-      <c r="J385" s="6"/>
+      <c r="J385" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
     </row>
@@ -16086,7 +16857,9 @@
       <c r="G386" s="3"/>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
-      <c r="J386" s="6"/>
+      <c r="J386" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
     </row>
@@ -16110,7 +16883,9 @@
       <c r="G387" s="3"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
-      <c r="J387" s="6"/>
+      <c r="J387" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
     </row>
@@ -16134,7 +16909,9 @@
       <c r="G388" s="3"/>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
-      <c r="J388" s="6"/>
+      <c r="J388" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
     </row>
@@ -16158,7 +16935,9 @@
       <c r="G389" s="3"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
-      <c r="J389" s="6"/>
+      <c r="J389" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
     </row>
@@ -16182,7 +16961,9 @@
       <c r="G390" s="3"/>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
-      <c r="J390" s="6"/>
+      <c r="J390" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
     </row>
@@ -16206,7 +16987,9 @@
       <c r="G391" s="3"/>
       <c r="H391" s="4"/>
       <c r="I391" s="4"/>
-      <c r="J391" s="6"/>
+      <c r="J391" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
     </row>
@@ -16230,7 +17013,9 @@
       <c r="G392" s="3"/>
       <c r="H392" s="4"/>
       <c r="I392" s="4"/>
-      <c r="J392" s="6"/>
+      <c r="J392" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
     </row>
@@ -16254,7 +17039,9 @@
       <c r="G393" s="3"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-      <c r="J393" s="6"/>
+      <c r="J393" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
     </row>
@@ -16278,7 +17065,9 @@
       <c r="G394" s="3"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
-      <c r="J394" s="6"/>
+      <c r="J394" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
     </row>
@@ -16302,7 +17091,9 @@
       <c r="G395" s="3"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-      <c r="J395" s="6"/>
+      <c r="J395" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
     </row>
@@ -16326,7 +17117,9 @@
       <c r="G396" s="3"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
-      <c r="J396" s="6"/>
+      <c r="J396" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
     </row>
@@ -16350,7 +17143,9 @@
       <c r="G397" s="3"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
-      <c r="J397" s="6"/>
+      <c r="J397" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
     </row>
@@ -16374,7 +17169,9 @@
       <c r="G398" s="3"/>
       <c r="H398" s="4"/>
       <c r="I398" s="4"/>
-      <c r="J398" s="6"/>
+      <c r="J398" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
     </row>
@@ -16398,7 +17195,9 @@
       <c r="G399" s="3"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
-      <c r="J399" s="6"/>
+      <c r="J399" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
     </row>
@@ -16422,7 +17221,9 @@
       <c r="G400" s="3"/>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
-      <c r="J400" s="6"/>
+      <c r="J400" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
     </row>
@@ -16446,7 +17247,9 @@
       <c r="G401" s="3"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-      <c r="J401" s="6"/>
+      <c r="J401" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
     </row>
@@ -16470,7 +17273,9 @@
       <c r="G402" s="3"/>
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
-      <c r="J402" s="6"/>
+      <c r="J402" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
     </row>
@@ -16494,7 +17299,9 @@
       <c r="G403" s="3"/>
       <c r="H403" s="4"/>
       <c r="I403" s="4"/>
-      <c r="J403" s="6"/>
+      <c r="J403" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
     </row>
@@ -16518,7 +17325,9 @@
       <c r="G404" s="3"/>
       <c r="H404" s="4"/>
       <c r="I404" s="4"/>
-      <c r="J404" s="6"/>
+      <c r="J404" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
     </row>
@@ -16542,7 +17351,9 @@
       <c r="G405" s="3"/>
       <c r="H405" s="4"/>
       <c r="I405" s="4"/>
-      <c r="J405" s="6"/>
+      <c r="J405" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
     </row>
@@ -16566,7 +17377,9 @@
       <c r="G406" s="3"/>
       <c r="H406" s="4"/>
       <c r="I406" s="4"/>
-      <c r="J406" s="6"/>
+      <c r="J406" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
     </row>
@@ -16590,7 +17403,9 @@
       <c r="G407" s="3"/>
       <c r="H407" s="4"/>
       <c r="I407" s="4"/>
-      <c r="J407" s="6"/>
+      <c r="J407" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
     </row>
@@ -16614,7 +17429,9 @@
       <c r="G408" s="3"/>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
-      <c r="J408" s="6"/>
+      <c r="J408" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
     </row>
@@ -16638,7 +17455,9 @@
       <c r="G409" s="3"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-      <c r="J409" s="6"/>
+      <c r="J409" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
     </row>
@@ -16662,7 +17481,9 @@
       <c r="G410" s="3"/>
       <c r="H410" s="4"/>
       <c r="I410" s="4"/>
-      <c r="J410" s="6"/>
+      <c r="J410" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
     </row>
@@ -16686,7 +17507,9 @@
       <c r="G411" s="3"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
-      <c r="J411" s="6"/>
+      <c r="J411" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
     </row>
@@ -16710,7 +17533,9 @@
       <c r="G412" s="3"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
-      <c r="J412" s="6"/>
+      <c r="J412" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
     </row>
@@ -16734,7 +17559,9 @@
       <c r="G413" s="3"/>
       <c r="H413" s="4"/>
       <c r="I413" s="4"/>
-      <c r="J413" s="6"/>
+      <c r="J413" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
     </row>
@@ -16758,7 +17585,9 @@
       <c r="G414" s="3"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
-      <c r="J414" s="6"/>
+      <c r="J414" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
     </row>
@@ -16784,7 +17613,9 @@
       <c r="I415" s="10" t="s">
         <v>1452</v>
       </c>
-      <c r="J415" s="6"/>
+      <c r="J415" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
     </row>
@@ -16810,7 +17641,9 @@
       <c r="I416" s="10" t="s">
         <v>1456</v>
       </c>
-      <c r="J416" s="6"/>
+      <c r="J416" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
     </row>
@@ -16834,7 +17667,9 @@
       <c r="G417" s="3"/>
       <c r="H417" s="4"/>
       <c r="I417" s="4"/>
-      <c r="J417" s="6"/>
+      <c r="J417" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
     </row>
@@ -16858,7 +17693,9 @@
       <c r="G418" s="3"/>
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
-      <c r="J418" s="6"/>
+      <c r="J418" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
     </row>
@@ -16882,7 +17719,9 @@
       <c r="G419" s="3"/>
       <c r="H419" s="4"/>
       <c r="I419" s="4"/>
-      <c r="J419" s="6"/>
+      <c r="J419" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
     </row>
@@ -16906,7 +17745,9 @@
       <c r="G420" s="3"/>
       <c r="H420" s="4"/>
       <c r="I420" s="4"/>
-      <c r="J420" s="6"/>
+      <c r="J420" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
     </row>
@@ -16930,7 +17771,9 @@
       <c r="G421" s="3"/>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
-      <c r="J421" s="6"/>
+      <c r="J421" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
     </row>
@@ -16954,7 +17797,9 @@
       <c r="G422" s="3"/>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
-      <c r="J422" s="6"/>
+      <c r="J422" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
     </row>
@@ -16978,7 +17823,9 @@
       <c r="G423" s="3"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
-      <c r="J423" s="6"/>
+      <c r="J423" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
     </row>
@@ -17002,7 +17849,9 @@
       <c r="G424" s="3"/>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
-      <c r="J424" s="6"/>
+      <c r="J424" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
     </row>
@@ -17026,7 +17875,9 @@
       <c r="G425" s="3"/>
       <c r="H425" s="4"/>
       <c r="I425" s="4"/>
-      <c r="J425" s="6"/>
+      <c r="J425" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
     </row>
@@ -17050,7 +17901,9 @@
       <c r="G426" s="3"/>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
-      <c r="J426" s="6"/>
+      <c r="J426" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
     </row>
@@ -17074,7 +17927,9 @@
       <c r="G427" s="3"/>
       <c r="H427" s="4"/>
       <c r="I427" s="4"/>
-      <c r="J427" s="6"/>
+      <c r="J427" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
     </row>
@@ -17098,7 +17953,9 @@
       <c r="G428" s="3"/>
       <c r="H428" s="4"/>
       <c r="I428" s="4"/>
-      <c r="J428" s="6"/>
+      <c r="J428" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
     </row>
@@ -17122,7 +17979,9 @@
       <c r="G429" s="3"/>
       <c r="H429" s="4"/>
       <c r="I429" s="4"/>
-      <c r="J429" s="6"/>
+      <c r="J429" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
     </row>
@@ -17146,7 +18005,9 @@
       <c r="G430" s="3"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
-      <c r="J430" s="6"/>
+      <c r="J430" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
     </row>
@@ -17170,7 +18031,9 @@
       <c r="G431" s="3"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-      <c r="J431" s="6"/>
+      <c r="J431" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
     </row>
@@ -17194,7 +18057,9 @@
       <c r="G432" s="3"/>
       <c r="H432" s="4"/>
       <c r="I432" s="4"/>
-      <c r="J432" s="6"/>
+      <c r="J432" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
     </row>
@@ -17218,7 +18083,9 @@
       <c r="G433" s="3"/>
       <c r="H433" s="4"/>
       <c r="I433" s="4"/>
-      <c r="J433" s="6"/>
+      <c r="J433" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
     </row>
@@ -17242,7 +18109,9 @@
       <c r="G434" s="3"/>
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
-      <c r="J434" s="6"/>
+      <c r="J434" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
     </row>
@@ -17266,7 +18135,9 @@
       <c r="G435" s="3"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-      <c r="J435" s="6"/>
+      <c r="J435" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
     </row>
@@ -17290,7 +18161,9 @@
       <c r="G436" s="3"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
-      <c r="J436" s="6"/>
+      <c r="J436" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
     </row>
@@ -17314,7 +18187,9 @@
       <c r="G437" s="3"/>
       <c r="H437" s="4"/>
       <c r="I437" s="4"/>
-      <c r="J437" s="6"/>
+      <c r="J437" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
     </row>
@@ -17338,7 +18213,9 @@
       <c r="G438" s="3"/>
       <c r="H438" s="4"/>
       <c r="I438" s="4"/>
-      <c r="J438" s="6"/>
+      <c r="J438" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
     </row>
@@ -17362,7 +18239,9 @@
       <c r="G439" s="3"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-      <c r="J439" s="6"/>
+      <c r="J439" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
     </row>
@@ -17386,7 +18265,9 @@
       <c r="G440" s="3"/>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
-      <c r="J440" s="6"/>
+      <c r="J440" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
     </row>
@@ -17410,7 +18291,9 @@
       <c r="G441" s="3"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
-      <c r="J441" s="6"/>
+      <c r="J441" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
     </row>
@@ -17434,7 +18317,9 @@
       <c r="G442" s="3"/>
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
-      <c r="J442" s="6"/>
+      <c r="J442" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
     </row>
@@ -17458,7 +18343,9 @@
       <c r="G443" s="3"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
-      <c r="J443" s="6"/>
+      <c r="J443" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
     </row>
@@ -17482,7 +18369,9 @@
       <c r="G444" s="3"/>
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
-      <c r="J444" s="6"/>
+      <c r="J444" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
     </row>
@@ -17506,7 +18395,9 @@
       <c r="G445" s="3"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
-      <c r="J445" s="6"/>
+      <c r="J445" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
     </row>
@@ -17530,7 +18421,9 @@
       <c r="G446" s="3"/>
       <c r="H446" s="4"/>
       <c r="I446" s="4"/>
-      <c r="J446" s="6"/>
+      <c r="J446" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
     </row>
@@ -17554,7 +18447,9 @@
       <c r="G447" s="3"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-      <c r="J447" s="6"/>
+      <c r="J447" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
     </row>
@@ -17578,7 +18473,9 @@
       <c r="G448" s="3"/>
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
-      <c r="J448" s="6"/>
+      <c r="J448" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
     </row>
@@ -17602,7 +18499,9 @@
       <c r="G449" s="3"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
-      <c r="J449" s="6"/>
+      <c r="J449" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
     </row>
@@ -17626,7 +18525,9 @@
       <c r="G450" s="3"/>
       <c r="H450" s="4"/>
       <c r="I450" s="4"/>
-      <c r="J450" s="6"/>
+      <c r="J450" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
     </row>
@@ -17650,7 +18551,9 @@
       <c r="G451" s="3"/>
       <c r="H451" s="4"/>
       <c r="I451" s="4"/>
-      <c r="J451" s="6"/>
+      <c r="J451" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
     </row>
@@ -17674,7 +18577,9 @@
       <c r="G452" s="3"/>
       <c r="H452" s="4"/>
       <c r="I452" s="4"/>
-      <c r="J452" s="6"/>
+      <c r="J452" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
     </row>
@@ -17698,7 +18603,9 @@
       <c r="G453" s="3"/>
       <c r="H453" s="4"/>
       <c r="I453" s="4"/>
-      <c r="J453" s="6"/>
+      <c r="J453" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
     </row>
@@ -17722,7 +18629,9 @@
       <c r="G454" s="3"/>
       <c r="H454" s="4"/>
       <c r="I454" s="4"/>
-      <c r="J454" s="6"/>
+      <c r="J454" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
     </row>
@@ -17746,7 +18655,9 @@
       <c r="G455" s="3"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-      <c r="J455" s="6"/>
+      <c r="J455" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
     </row>
@@ -17770,7 +18681,9 @@
       <c r="G456" s="3"/>
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
-      <c r="J456" s="6"/>
+      <c r="J456" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
     </row>
@@ -17794,7 +18707,9 @@
       <c r="G457" s="3"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-      <c r="J457" s="6"/>
+      <c r="J457" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
     </row>
@@ -17818,7 +18733,9 @@
       <c r="G458" s="3"/>
       <c r="H458" s="4"/>
       <c r="I458" s="4"/>
-      <c r="J458" s="6"/>
+      <c r="J458" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
     </row>
@@ -17842,7 +18759,9 @@
       <c r="G459" s="3"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-      <c r="J459" s="6"/>
+      <c r="J459" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
     </row>
@@ -17866,7 +18785,9 @@
       <c r="G460" s="3"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
-      <c r="J460" s="6"/>
+      <c r="J460" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
     </row>
@@ -17890,7 +18811,9 @@
       <c r="G461" s="3"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-      <c r="J461" s="6"/>
+      <c r="J461" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
     </row>
@@ -17914,7 +18837,9 @@
       <c r="G462" s="3"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
-      <c r="J462" s="6"/>
+      <c r="J462" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
     </row>
@@ -17938,7 +18863,9 @@
       <c r="G463" s="3"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-      <c r="J463" s="6"/>
+      <c r="J463" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
     </row>
@@ -17962,7 +18889,9 @@
       <c r="G464" s="3"/>
       <c r="H464" s="4"/>
       <c r="I464" s="4"/>
-      <c r="J464" s="6"/>
+      <c r="J464" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
     </row>
@@ -17986,7 +18915,9 @@
       <c r="G465" s="3"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
-      <c r="J465" s="6"/>
+      <c r="J465" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
     </row>
@@ -18010,7 +18941,9 @@
       <c r="G466" s="3"/>
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
-      <c r="J466" s="6"/>
+      <c r="J466" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
     </row>
@@ -18034,7 +18967,9 @@
       <c r="G467" s="3"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
-      <c r="J467" s="6"/>
+      <c r="J467" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
     </row>
@@ -18058,7 +18993,9 @@
       <c r="G468" s="3"/>
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
-      <c r="J468" s="6"/>
+      <c r="J468" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
     </row>
@@ -18082,7 +19019,9 @@
       <c r="G469" s="3"/>
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
-      <c r="J469" s="6"/>
+      <c r="J469" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
     </row>
@@ -18106,7 +19045,9 @@
       <c r="G470" s="3"/>
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
-      <c r="J470" s="6"/>
+      <c r="J470" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
     </row>
@@ -18130,7 +19071,9 @@
       <c r="G471" s="3"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
-      <c r="J471" s="6"/>
+      <c r="J471" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
     </row>
@@ -18154,7 +19097,9 @@
       <c r="G472" s="3"/>
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
-      <c r="J472" s="6"/>
+      <c r="J472" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
     </row>
@@ -18178,7 +19123,9 @@
       <c r="G473" s="3"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
-      <c r="J473" s="6"/>
+      <c r="J473" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
     </row>
@@ -18202,7 +19149,9 @@
       <c r="G474" s="3"/>
       <c r="H474" s="4"/>
       <c r="I474" s="4"/>
-      <c r="J474" s="6"/>
+      <c r="J474" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
     </row>
@@ -18226,7 +19175,9 @@
       <c r="G475" s="3"/>
       <c r="H475" s="4"/>
       <c r="I475" s="4"/>
-      <c r="J475" s="6"/>
+      <c r="J475" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
     </row>
@@ -18250,7 +19201,9 @@
       <c r="G476" s="3"/>
       <c r="H476" s="4"/>
       <c r="I476" s="4"/>
-      <c r="J476" s="6"/>
+      <c r="J476" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
     </row>
@@ -18274,7 +19227,9 @@
       <c r="G477" s="3"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
-      <c r="J477" s="6"/>
+      <c r="J477" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
     </row>
@@ -18298,7 +19253,9 @@
       <c r="G478" s="3"/>
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
-      <c r="J478" s="6"/>
+      <c r="J478" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
     </row>
@@ -18322,7 +19279,9 @@
       <c r="G479" s="3"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
-      <c r="J479" s="6"/>
+      <c r="J479" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
     </row>
@@ -18346,7 +19305,9 @@
       <c r="G480" s="3"/>
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
-      <c r="J480" s="6"/>
+      <c r="J480" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
     </row>
@@ -18370,7 +19331,9 @@
       <c r="G481" s="3"/>
       <c r="H481" s="4"/>
       <c r="I481" s="4"/>
-      <c r="J481" s="6"/>
+      <c r="J481" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
     </row>
@@ -18394,7 +19357,9 @@
       <c r="G482" s="3"/>
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
-      <c r="J482" s="6"/>
+      <c r="J482" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
     </row>
@@ -18418,7 +19383,9 @@
       <c r="G483" s="3"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
-      <c r="J483" s="6"/>
+      <c r="J483" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
     </row>
@@ -18442,7 +19409,9 @@
       <c r="G484" s="3"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
-      <c r="J484" s="6"/>
+      <c r="J484" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
     </row>
@@ -18466,7 +19435,9 @@
       <c r="G485" s="3"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-      <c r="J485" s="6"/>
+      <c r="J485" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
     </row>
@@ -18490,7 +19461,9 @@
       <c r="G486" s="3"/>
       <c r="H486" s="4"/>
       <c r="I486" s="4"/>
-      <c r="J486" s="6"/>
+      <c r="J486" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
     </row>
@@ -18514,7 +19487,9 @@
       <c r="G487" s="3"/>
       <c r="H487" s="4"/>
       <c r="I487" s="4"/>
-      <c r="J487" s="6"/>
+      <c r="J487" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
     </row>
@@ -18538,7 +19513,9 @@
       <c r="G488" s="3"/>
       <c r="H488" s="4"/>
       <c r="I488" s="4"/>
-      <c r="J488" s="6"/>
+      <c r="J488" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
     </row>
@@ -18562,7 +19539,9 @@
       <c r="G489" s="3"/>
       <c r="H489" s="4"/>
       <c r="I489" s="4"/>
-      <c r="J489" s="6"/>
+      <c r="J489" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
     </row>
@@ -18588,7 +19567,9 @@
       <c r="I490" s="10" t="s">
         <v>1452</v>
       </c>
-      <c r="J490" s="6"/>
+      <c r="J490" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
     </row>
@@ -18612,7 +19593,9 @@
       <c r="G491" s="3"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
-      <c r="J491" s="6"/>
+      <c r="J491" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
     </row>
@@ -18636,7 +19619,9 @@
       <c r="G492" s="3"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
-      <c r="J492" s="6"/>
+      <c r="J492" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>
     </row>
@@ -18660,7 +19645,9 @@
       <c r="G493" s="3"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
-      <c r="J493" s="6"/>
+      <c r="J493" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
     </row>
@@ -18684,7 +19671,9 @@
       <c r="G494" s="3"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
-      <c r="J494" s="6"/>
+      <c r="J494" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
     </row>
@@ -18708,7 +19697,9 @@
       <c r="G495" s="3"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
-      <c r="J495" s="6"/>
+      <c r="J495" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
     </row>
@@ -18732,7 +19723,9 @@
       <c r="G496" s="3"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
-      <c r="J496" s="6"/>
+      <c r="J496" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
     </row>
@@ -18756,7 +19749,9 @@
       <c r="G497" s="3"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
-      <c r="J497" s="6"/>
+      <c r="J497" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
     </row>
@@ -18780,7 +19775,9 @@
       <c r="G498" s="3"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
-      <c r="J498" s="6"/>
+      <c r="J498" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
     </row>
@@ -18804,7 +19801,9 @@
       <c r="G499" s="3"/>
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
-      <c r="J499" s="6"/>
+      <c r="J499" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
     </row>
@@ -18828,7 +19827,9 @@
       <c r="G500" s="3"/>
       <c r="H500" s="4"/>
       <c r="I500" s="4"/>
-      <c r="J500" s="6"/>
+      <c r="J500" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
     </row>
@@ -18852,7 +19853,9 @@
       <c r="G501" s="3"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
-      <c r="J501" s="6"/>
+      <c r="J501" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
     </row>
@@ -18876,7 +19879,9 @@
       <c r="G502" s="3"/>
       <c r="H502" s="4"/>
       <c r="I502" s="4"/>
-      <c r="J502" s="6"/>
+      <c r="J502" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
     </row>
@@ -18902,7 +19907,9 @@
       <c r="G503" s="3"/>
       <c r="H503" s="4"/>
       <c r="I503" s="4"/>
-      <c r="J503" s="6"/>
+      <c r="J503" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
     </row>
@@ -18928,7 +19935,9 @@
       <c r="G504" s="3"/>
       <c r="H504" s="4"/>
       <c r="I504" s="4"/>
-      <c r="J504" s="6"/>
+      <c r="J504" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
     </row>
@@ -18954,7 +19963,9 @@
       <c r="G505" s="3"/>
       <c r="H505" s="4"/>
       <c r="I505" s="4"/>
-      <c r="J505" s="6"/>
+      <c r="J505" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
     </row>
@@ -18984,7 +19995,9 @@
         <v>1727</v>
       </c>
       <c r="I506" s="4"/>
-      <c r="J506" s="6"/>
+      <c r="J506" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
     </row>
@@ -19008,7 +20021,9 @@
       <c r="G507" s="3"/>
       <c r="H507" s="4"/>
       <c r="I507" s="4"/>
-      <c r="J507" s="6"/>
+      <c r="J507" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
     </row>
@@ -19032,7 +20047,9 @@
       <c r="G508" s="3"/>
       <c r="H508" s="4"/>
       <c r="I508" s="4"/>
-      <c r="J508" s="6"/>
+      <c r="J508" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K508" s="7"/>
       <c r="L508" s="7"/>
     </row>
@@ -19056,7 +20073,9 @@
       <c r="G509" s="3"/>
       <c r="H509" s="4"/>
       <c r="I509" s="4"/>
-      <c r="J509" s="6"/>
+      <c r="J509" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K509" s="7"/>
       <c r="L509" s="7"/>
     </row>
@@ -19080,7 +20099,9 @@
       <c r="G510" s="3"/>
       <c r="H510" s="4"/>
       <c r="I510" s="4"/>
-      <c r="J510" s="6"/>
+      <c r="J510" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
     </row>
@@ -19104,7 +20125,9 @@
       <c r="G511" s="3"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
-      <c r="J511" s="6"/>
+      <c r="J511" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
     </row>
@@ -19128,7 +20151,9 @@
       <c r="G512" s="3"/>
       <c r="H512" s="4"/>
       <c r="I512" s="4"/>
-      <c r="J512" s="6"/>
+      <c r="J512" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
     </row>
@@ -19152,7 +20177,9 @@
       <c r="G513" s="3"/>
       <c r="H513" s="4"/>
       <c r="I513" s="4"/>
-      <c r="J513" s="6"/>
+      <c r="J513" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
     </row>
@@ -19176,7 +20203,9 @@
       <c r="G514" s="3"/>
       <c r="H514" s="4"/>
       <c r="I514" s="4"/>
-      <c r="J514" s="6"/>
+      <c r="J514" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
     </row>
@@ -19200,7 +20229,9 @@
       <c r="G515" s="3"/>
       <c r="H515" s="4"/>
       <c r="I515" s="4"/>
-      <c r="J515" s="6"/>
+      <c r="J515" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
     </row>
@@ -19228,7 +20259,9 @@
         <v>1758</v>
       </c>
       <c r="I516" s="4"/>
-      <c r="J516" s="6"/>
+      <c r="J516" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
     </row>
@@ -19252,7 +20285,9 @@
       <c r="G517" s="3"/>
       <c r="H517" s="4"/>
       <c r="I517" s="4"/>
-      <c r="J517" s="6"/>
+      <c r="J517" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
     </row>
@@ -19280,7 +20315,9 @@
         <v>1765</v>
       </c>
       <c r="I518" s="4"/>
-      <c r="J518" s="6"/>
+      <c r="J518" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
     </row>
@@ -19304,7 +20341,9 @@
       <c r="G519" s="3"/>
       <c r="H519" s="4"/>
       <c r="I519" s="4"/>
-      <c r="J519" s="6"/>
+      <c r="J519" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
     </row>
@@ -19328,7 +20367,9 @@
       <c r="G520" s="3"/>
       <c r="H520" s="4"/>
       <c r="I520" s="4"/>
-      <c r="J520" s="6"/>
+      <c r="J520" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
     </row>
@@ -19352,7 +20393,9 @@
       <c r="G521" s="3"/>
       <c r="H521" s="4"/>
       <c r="I521" s="4"/>
-      <c r="J521" s="6"/>
+      <c r="J521" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
     </row>
@@ -19376,7 +20419,9 @@
       <c r="G522" s="3"/>
       <c r="H522" s="4"/>
       <c r="I522" s="4"/>
-      <c r="J522" s="6"/>
+      <c r="J522" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K522" s="7"/>
       <c r="L522" s="7"/>
     </row>
@@ -19400,7 +20445,9 @@
       <c r="G523" s="3"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
-      <c r="J523" s="6"/>
+      <c r="J523" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
     </row>
@@ -19424,7 +20471,9 @@
       <c r="G524" s="3"/>
       <c r="H524" s="4"/>
       <c r="I524" s="4"/>
-      <c r="J524" s="6"/>
+      <c r="J524" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K524" s="7"/>
       <c r="L524" s="7"/>
     </row>
@@ -19448,7 +20497,9 @@
       <c r="G525" s="3"/>
       <c r="H525" s="4"/>
       <c r="I525" s="4"/>
-      <c r="J525" s="6"/>
+      <c r="J525" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K525" s="7"/>
       <c r="L525" s="7"/>
     </row>
@@ -19472,7 +20523,9 @@
       <c r="G526" s="3"/>
       <c r="H526" s="4"/>
       <c r="I526" s="4"/>
-      <c r="J526" s="6"/>
+      <c r="J526" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K526" s="7"/>
       <c r="L526" s="7"/>
     </row>
@@ -19498,7 +20551,9 @@
       <c r="G527" s="3"/>
       <c r="H527" s="4"/>
       <c r="I527" s="4"/>
-      <c r="J527" s="6"/>
+      <c r="J527" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K527" s="7"/>
       <c r="L527" s="7"/>
     </row>
@@ -19522,7 +20577,9 @@
       <c r="G528" s="3"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
-      <c r="J528" s="6"/>
+      <c r="J528" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
     </row>
@@ -19546,7 +20603,9 @@
       <c r="G529" s="3"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
-      <c r="J529" s="6"/>
+      <c r="J529" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K529" s="7"/>
       <c r="L529" s="7"/>
     </row>
@@ -19570,7 +20629,9 @@
       <c r="G530" s="3"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
-      <c r="J530" s="6"/>
+      <c r="J530" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
     </row>
@@ -19594,7 +20655,9 @@
       <c r="G531" s="3"/>
       <c r="H531" s="4"/>
       <c r="I531" s="4"/>
-      <c r="J531" s="6"/>
+      <c r="J531" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
     </row>
@@ -19618,7 +20681,9 @@
       <c r="G532" s="3"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
-      <c r="J532" s="6"/>
+      <c r="J532" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K532" s="7"/>
       <c r="L532" s="7"/>
     </row>
@@ -19642,7 +20707,9 @@
       <c r="G533" s="3"/>
       <c r="H533" s="4"/>
       <c r="I533" s="4"/>
-      <c r="J533" s="6"/>
+      <c r="J533" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K533" s="7"/>
       <c r="L533" s="7"/>
     </row>
@@ -19666,7 +20733,9 @@
       <c r="G534" s="3"/>
       <c r="H534" s="4"/>
       <c r="I534" s="4"/>
-      <c r="J534" s="6"/>
+      <c r="J534" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K534" s="7"/>
       <c r="L534" s="7"/>
     </row>
@@ -19690,7 +20759,9 @@
       <c r="G535" s="3"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
-      <c r="J535" s="6"/>
+      <c r="J535" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
     </row>
@@ -19714,7 +20785,9 @@
       <c r="G536" s="3"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
-      <c r="J536" s="6"/>
+      <c r="J536" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K536" s="7"/>
       <c r="L536" s="7"/>
     </row>
@@ -19740,7 +20813,9 @@
       <c r="I537" s="10" t="s">
         <v>1823</v>
       </c>
-      <c r="J537" s="6"/>
+      <c r="J537" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K537" s="7"/>
       <c r="L537" s="7"/>
     </row>
@@ -19764,7 +20839,9 @@
       <c r="G538" s="3"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
-      <c r="J538" s="6"/>
+      <c r="J538" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K538" s="7"/>
       <c r="L538" s="7"/>
     </row>
@@ -19788,14 +20865,19 @@
       <c r="G539" s="3"/>
       <c r="H539" s="4"/>
       <c r="I539" s="4"/>
-      <c r="J539" s="6"/>
+      <c r="J539" s="6" t="s">
+        <v>1842</v>
+      </c>
       <c r="K539" s="7"/>
       <c r="L539" s="7"/>
+    </row>
+    <row r="1048576" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J1048576" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L539" xr:uid="{7CF339A9-FF88-447A-9833-43357AC94A3F}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J539" xr:uid="{78DA4C87-DFA3-44D0-A14F-F16F357F6778}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1048576 J2:J539" xr:uid="{78DA4C87-DFA3-44D0-A14F-F16F357F6778}">
       <formula1>"OK,Use my Spanish,Keep current,Discuss"</formula1>
     </dataValidation>
   </dataValidations>
